--- a/volunteer_registration_forms/016_ethics_review_board_volunteer_registration--volunteer_registration_forms.xlsx
+++ b/volunteer_registration_forms/016_ethics_review_board_volunteer_registration--volunteer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'ethics_review_board_1',_'value':_1}</t>
+          <t>ethics_review_board_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Ethics Review Board 1', 'value': 1}</t>
+          <t>Ethics Review Board 1</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'ethics_review_board_2',_'value':_2}</t>
+          <t>ethics_review_board_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Ethics Review Board 2', 'value': 2}</t>
+          <t>Ethics Review Board 2</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'university',_'value':_'university'}</t>
+          <t>university</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'University', 'value': 'University'}</t>
+          <t>University</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'hospital',_'value':_'hospital'}</t>
+          <t>hospital</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Hospital', 'value': 'Hospital'}</t>
+          <t>Hospital</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'non-profit',_'value':_'non-profit'}</t>
+          <t>non-profit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Profit', 'value': 'Non-Profit'}</t>
+          <t>Non-Profit</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'i_consent_to_serve_on_an_ethics_review_board',_'value':_1}</t>
+          <t>i_consent_to_serve_on_an_ethics_review_board</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'I consent to serve on an Ethics Review Board', 'value': 1}</t>
+          <t>I consent to serve on an Ethics Review Board</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'i_do_not_consent_to_serve_on_an_ethics_review_board',_'value':_2}</t>
+          <t>i_do_not_consent_to_serve_on_an_ethics_review_board</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'I do not consent to serve on an Ethics Review Board', 'value': 2}</t>
+          <t>I do not consent to serve on an Ethics Review Board</t>
         </is>
       </c>
     </row>
